--- a/artfynd/A 15447-2024 artfynd.xlsx
+++ b/artfynd/A 15447-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY496"/>
+  <dimension ref="A1:AY497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52707,6 +52707,118 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>119475805</v>
+      </c>
+      <c r="B497" t="n">
+        <v>90043</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr"/>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>828377</v>
+      </c>
+      <c r="R497" t="n">
+        <v>7328407</v>
+      </c>
+      <c r="S497" t="n">
+        <v>1</v>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB497" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD497" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE497" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG497" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT497" t="inlineStr"/>
+      <c r="AW497" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AX497" t="inlineStr">
+        <is>
+          <t>Lena Bondestad, Berth-Ove Lindström</t>
+        </is>
+      </c>
+      <c r="AY497" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15447-2024 artfynd.xlsx
+++ b/artfynd/A 15447-2024 artfynd.xlsx
@@ -52712,7 +52712,7 @@
         <v>119475805</v>
       </c>
       <c r="B497" t="n">
-        <v>90043</v>
+        <v>90060</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>

--- a/artfynd/A 15447-2024 artfynd.xlsx
+++ b/artfynd/A 15447-2024 artfynd.xlsx
@@ -1535,11 +1535,11 @@
         <v>117164348</v>
       </c>
       <c r="B10" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4187,11 +4187,11 @@
         <v>117164339</v>
       </c>
       <c r="B36" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7349,11 +7349,11 @@
         <v>117164341</v>
       </c>
       <c r="B67" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8573,11 +8573,11 @@
         <v>117164345</v>
       </c>
       <c r="B79" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8675,11 +8675,11 @@
         <v>117164346</v>
       </c>
       <c r="B80" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10103,11 +10103,11 @@
         <v>117164344</v>
       </c>
       <c r="B94" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10715,11 +10715,11 @@
         <v>117164342</v>
       </c>
       <c r="B100" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13775,11 +13775,11 @@
         <v>117164343</v>
       </c>
       <c r="B130" t="n">
-        <v>56494</v>
+        <v>56593</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -32527,11 +32527,11 @@
         <v>119413124</v>
       </c>
       <c r="B307" t="n">
-        <v>56522</v>
+        <v>56593</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">

--- a/artfynd/A 15447-2024 artfynd.xlsx
+++ b/artfynd/A 15447-2024 artfynd.xlsx
@@ -1535,11 +1535,11 @@
         <v>117164348</v>
       </c>
       <c r="B10" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4187,11 +4187,11 @@
         <v>117164339</v>
       </c>
       <c r="B36" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7349,11 +7349,11 @@
         <v>117164341</v>
       </c>
       <c r="B67" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8573,11 +8573,11 @@
         <v>117164345</v>
       </c>
       <c r="B79" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8675,11 +8675,11 @@
         <v>117164346</v>
       </c>
       <c r="B80" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10103,11 +10103,11 @@
         <v>117164344</v>
       </c>
       <c r="B94" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10715,11 +10715,11 @@
         <v>117164342</v>
       </c>
       <c r="B100" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13775,11 +13775,11 @@
         <v>117164343</v>
       </c>
       <c r="B130" t="n">
-        <v>56593</v>
+        <v>56494</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -32527,11 +32527,11 @@
         <v>119413124</v>
       </c>
       <c r="B307" t="n">
-        <v>56593</v>
+        <v>56522</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
